--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. Click Close Welcome Banner on the Welcome banner. 2. Click Me want it! on the cookie banner.</t>
+          <t>1. Click Close Welcome Banner on the Welcome banner. 2. Click Me want it! (Dismiss cookie message) on the cookie banner.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>User is redirected to the main page. Account menu shows the user email.</t>
+          <t>User is redirected to the search page with the product list. Account menu shows the user email.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should log in with valid credentials</t>
+          <t>tests/login.spec.js › should handle login: valid credentials</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should reject login: wrong password</t>
+          <t>tests/login.spec.js › should handle login: wrong password</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Login page is open</t>
+          <t>Registered test user exists. Banners are dismissed. Login form is open.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should reject login: non-existing email</t>
+          <t>tests/login.spec.js › should handle login: non-existing email</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Login page is open</t>
+          <t>Banners are dismissed. Login form is open.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should block login with empty email</t>
+          <t>tests/login.spec.js › should handle login: empty email</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Login page is open</t>
+          <t>Registered test user exists. Banners are dismissed. Login form is open.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Login page is open</t>
+          <t>Banners are dismissed. Login form is open.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Main page is open</t>
+          <t>Banners are dismissed. Main page is open.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Main page is open</t>
+          <t>Banners are dismissed. Main page is open.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>tests/popups.spec.js › should dismiss popups and show app heading</t>
+          <t>tests/popups.spec.js › should show app name after popups are dismissed</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. Open Account. 2. Click Login. 3. Enter valid email and password. 4. Click Log in.</t>
+          <t>1. Open Account. 2. Click Login. 3. Enter valid email and password. 4. Click Login.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should handle login: valid credentials</t>
+          <t>tests/login.spec.js › should log in with valid credentials</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. Open Account. 2. Click Login. 3. Enter valid email and a wrong password. 4. Click Log in.</t>
+          <t>1. Open Account. 2. Click Login. 3. Enter valid email and a wrong password. 4. Click Login.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should handle login: wrong password</t>
+          <t>tests/login.spec.js › should show error for wrong password</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. Enter an email that is not registered. 2. Enter any password. 3. Click Log in.</t>
+          <t>1. Enter an email that is not registered. 2. Enter any password. 3. Click Login.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should handle login: non-existing email</t>
+          <t>tests/login.spec.js › should show error for non-existing email</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Message Please provide an email address. is shown. Log in button is disabled.</t>
+          <t>Message Please provide an email address. is shown. Login button is disabled.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>tests/login.spec.js › should handle login: empty email</t>
+          <t>tests/login.spec.js › should block login with empty email</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Log in button is disabled.</t>
+          <t>Login button is disabled.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>tests/products.spec.js › should show product cards on the main page</t>
+          <t>tests/products.spec.js › should show product cards with Add to Basket button on the main page</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Search results contain 3 product cards.</t>
+          <t>Product card Apple Juice (1000ml) is shown in the search results.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>tests/products.spec.js › should find products by existing query</t>
+          <t>tests/products.spec.js › should show matching product for existing search query</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>tests/products.spec.js › should show no results for missing query</t>
+          <t>tests/products.spec.js › should show no results message for missing search query</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. Click Your Basket.</t>
+          <t>1. Click the basket icon (Show the shopping cart).</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>tests/basket.spec.js › should show empty basket for a new user</t>
+          <t>tests/basket.spec.js › should show no products in basket for a new user</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>tests/basket.spec.js › should add product to basket and show it in basket</t>
+          <t>tests/basket.spec.js › should show added product and total price in basket</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. Click Your Basket.</t>
+          <t>1. Click the basket icon (Show the shopping cart).</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>tests/basket.spec.js › should add product to basket and show it in basket</t>
+          <t>tests/basket.spec.js › should show added product and total price in basket</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>tests/basket.spec.js › should increase quantity when adding the same product twice</t>
+          <t>tests/basket.spec.js › should double the total price when the same product is added twice</t>
         </is>
       </c>
     </row>
